--- a/Documentation/Week 6/Booked Hours/Booked_Hours_Dylan.xlsx
+++ b/Documentation/Week 6/Booked Hours/Booked_Hours_Dylan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 6/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684EF329-DADD-4893-8492-631861C36E7C}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977F3D22-AA9F-4603-939A-0D486ADC121B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <r>
       <t xml:space="preserve">CITS3200 Project Billed Hours Record for &lt;Dylan Hu&gt;
@@ -1459,6 +1459,9 @@
       <c r="E22" s="5">
         <v>0.98263888888888884</v>
       </c>
+      <c r="F22" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G22" s="6">
         <f t="shared" si="0"/>
         <v>0.25000000011641532</v>

--- a/Documentation/Week 6/Booked Hours/Booked_Hours_Dylan.xlsx
+++ b/Documentation/Week 6/Booked Hours/Booked_Hours_Dylan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 6/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{977F3D22-AA9F-4603-939A-0D486ADC121B}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="8_{C839D0D7-89B3-4B1F-A7FA-FAF46048CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D55FB07-AB08-4E6B-BF57-9C9706B127A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="23">
   <si>
     <r>
       <t xml:space="preserve">CITS3200 Project Billed Hours Record for &lt;Dylan Hu&gt;
@@ -116,7 +116,10 @@
     <t>Auditor meeting</t>
   </si>
   <si>
-    <t>Planning and allocating tasks</t>
+    <t>Planning and allocating sub-team tasks</t>
+  </si>
+  <si>
+    <t>Documenting team and auditor minutes</t>
   </si>
 </sst>
 </file>
@@ -357,6 +360,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -375,14 +386,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -816,36 +819,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="12"/>
       <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
     </row>
@@ -865,7 +868,7 @@
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1303,7 +1306,7 @@
         <v>18</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" ref="G17:G20" si="5">IF(I17&gt;0,I17,IF(I17=0, " ", "ERROR"))</f>
+        <f t="shared" ref="G17:G19" si="5">IF(I17&gt;0,I17,IF(I17=0, " ", "ERROR"))</f>
         <v>0.49999999988358468</v>
       </c>
       <c r="H17" s="1">
@@ -1352,30 +1355,30 @@
         <v>6</v>
       </c>
       <c r="B19" s="4">
-        <v>44798</v>
+        <v>44797</v>
       </c>
       <c r="C19" s="5">
-        <v>0.45833333333333331</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D19" s="4">
-        <v>44798</v>
+        <v>44797</v>
       </c>
       <c r="E19" s="5">
-        <v>0.48958333333333331</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G19" s="6">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
       <c r="H19" s="1">
-        <f>IF(AND(G19&lt;&gt;" ",G19&lt;&gt;"ERROR",H16&lt;&gt;" ", H16&lt;&gt;"ERROR"),G19+H16," ")</f>
-        <v>17.749999999708962</v>
+        <f t="shared" si="2"/>
+        <v>18.499999999534339</v>
       </c>
       <c r="I19" s="1">
-        <f t="shared" si="1"/>
+        <f>((D20+E20)-(B20+C20))*24</f>
         <v>0.75</v>
       </c>
     </row>
@@ -1387,27 +1390,27 @@
         <v>44798</v>
       </c>
       <c r="C20" s="5">
-        <v>0.5</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D20" s="4">
         <v>44798</v>
       </c>
       <c r="E20" s="5">
-        <v>0.53125</v>
+        <v>0.48958333333333331</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="5"/>
+        <f>IF(I19&gt;0,I19,IF(I19=0, " ", "ERROR"))</f>
         <v>0.75</v>
       </c>
       <c r="H20" s="1">
-        <f t="shared" ref="H20" si="7">IF(AND(G20&lt;&gt;" ",G20&lt;&gt;"ERROR",H19&lt;&gt;" ", H19&lt;&gt;"ERROR"),G20+H19," ")</f>
-        <v>18.499999999708962</v>
+        <f t="shared" si="2"/>
+        <v>19.249999999534339</v>
       </c>
       <c r="I20" s="1">
-        <f t="shared" si="1"/>
+        <f>((D21+E21)-(B21+C21))*24</f>
         <v>0.75</v>
       </c>
     </row>
@@ -1419,28 +1422,28 @@
         <v>44798</v>
       </c>
       <c r="C21" s="5">
-        <v>0.54166666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="4">
         <v>44798</v>
       </c>
       <c r="E21" s="5">
-        <v>0.57291666666666663</v>
+        <v>0.53125</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" ref="G21" si="8">IF(I21&gt;0,I21,IF(I21=0, " ", "ERROR"))</f>
+        <f>IF(I20&gt;0,I20,IF(I20=0, " ", "ERROR"))</f>
         <v>0.75</v>
       </c>
       <c r="H21" s="1">
-        <f t="shared" ref="H21" si="9">IF(AND(G21&lt;&gt;" ",G21&lt;&gt;"ERROR",H20&lt;&gt;" ", H20&lt;&gt;"ERROR"),G21+H20," ")</f>
-        <v>19.249999999708962</v>
+        <f t="shared" si="2"/>
+        <v>19.999999999534339</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
+        <f>((D23+E23)-(B23+C23))*24</f>
+        <v>1.0000000001164153</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
@@ -1448,67 +1451,95 @@
         <v>6</v>
       </c>
       <c r="B22" s="4">
-        <v>44799</v>
+        <v>44798</v>
       </c>
       <c r="C22" s="5">
-        <v>0.97222222222222221</v>
+        <v>0.53125</v>
       </c>
       <c r="D22" s="4">
-        <v>44799</v>
+        <v>44798</v>
       </c>
       <c r="E22" s="5">
-        <v>0.98263888888888884</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="0"/>
-        <v>0.25000000011641532</v>
+        <f>IF(I21&gt;0,I21,IF(I21=0, " ", "ERROR"))</f>
+        <v>1.0000000001164153</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="2"/>
-        <v>19.499999999825377</v>
+        <v>20.999999999650754</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="1"/>
+        <f>((D24+E24)-(B24+C24))*24</f>
         <v>0.25000000011641532</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="G23" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H23" s="1" t="str">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4">
+        <v>44798</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D23" s="4">
+        <v>44798</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="6">
+        <f>IF(I21&gt;0,I21,IF(I21=0, " ", "ERROR"))</f>
+        <v>1.0000000001164153</v>
+      </c>
+      <c r="H23" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I23" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21.999999999767169</v>
+      </c>
+      <c r="I23" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="G24" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H24" s="1" t="str">
+      <c r="A24" s="1">
+        <v>6</v>
+      </c>
+      <c r="B24" s="4">
+        <v>44799</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="D24" s="4">
+        <v>44799</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="6">
+        <f>IF(I22&gt;0,I22,IF(I22=0, " ", "ERROR"))</f>
+        <v>0.25000000011641532</v>
+      </c>
+      <c r="H24" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I24" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22.249999999883585</v>
+      </c>
+      <c r="I24" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1520,85 +1551,33 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H25" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
       <c r="I25" s="1">
-        <f t="shared" si="1"/>
+        <f>((D25+E25)-(B25+C25))*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="G26" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H26" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I26" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="I26" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="G27" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H27" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I27" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="I27" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="G28" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H28" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I28" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="I28" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="G29" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H29" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="I29" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="I29" s="1" t="e">
+        <f>((#REF!+#REF!)-(#REF!+#REF!))*24</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1610,9 +1589,9 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="H30" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+      <c r="H30" s="1" t="e">
+        <f>IF(AND(G30&lt;&gt;" ",G30&lt;&gt;"ERROR",#REF!&lt;&gt;" ",#REF!&lt;&gt; "ERROR"),G30+#REF!," ")</f>
+        <v>#REF!</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="1"/>
@@ -1623,14 +1602,14 @@
       <c r="A31" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="12"/>
+      <c r="D31" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="8" t="s">
         <v>4</v>
       </c>
@@ -1673,12 +1652,12 @@
       <c r="D33" s="4"/>
       <c r="E33" s="5"/>
       <c r="G33" s="6" t="str">
-        <f t="shared" ref="G33:G64" si="10">IF(I33&gt;0,I33,IF(I33=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H33" s="1" t="str">
+        <f t="shared" ref="G33:G64" si="7">IF(I33&gt;0,I33,IF(I33=0, " ", "ERROR"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H33" s="1" t="e">
         <f>IF(AND(G33&lt;&gt;" ",G33&lt;&gt;"ERROR",H30&lt;&gt;" ", H30&lt;&gt;"ERROR"),G33+H30," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>#REF!</v>
       </c>
       <c r="I33" s="1">
         <f t="shared" si="1"/>
@@ -1691,12 +1670,12 @@
       <c r="D34" s="4"/>
       <c r="E34" s="5"/>
       <c r="G34" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H34" s="1" t="str">
-        <f t="shared" ref="H34:H64" si="11">IF(AND(G34&lt;&gt;" ",G34&lt;&gt;"ERROR",H33&lt;&gt;" ", H33&lt;&gt;"ERROR"),G34+H33," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H34" s="1" t="e">
+        <f t="shared" ref="H34:H64" si="8">IF(AND(G34&lt;&gt;" ",G34&lt;&gt;"ERROR",H33&lt;&gt;" ", H33&lt;&gt;"ERROR"),G34+H33," ")</f>
+        <v>#REF!</v>
       </c>
       <c r="I34" s="1">
         <f t="shared" si="1"/>
@@ -1709,12 +1688,12 @@
       <c r="D35" s="4"/>
       <c r="E35" s="5"/>
       <c r="G35" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H35" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H35" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I35" s="1">
         <f t="shared" si="1"/>
@@ -1727,12 +1706,12 @@
       <c r="D36" s="4"/>
       <c r="E36" s="5"/>
       <c r="G36" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H36" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H36" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I36" s="1">
         <f t="shared" si="1"/>
@@ -1745,12 +1724,12 @@
       <c r="D37" s="4"/>
       <c r="E37" s="5"/>
       <c r="G37" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H37" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H37" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I37" s="1">
         <f t="shared" si="1"/>
@@ -1763,12 +1742,12 @@
       <c r="D38" s="4"/>
       <c r="E38" s="5"/>
       <c r="G38" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H38" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H38" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I38" s="1">
         <f t="shared" si="1"/>
@@ -1781,12 +1760,12 @@
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
       <c r="G39" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H39" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H39" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I39" s="1">
         <f t="shared" si="1"/>
@@ -1799,12 +1778,12 @@
       <c r="D40" s="4"/>
       <c r="E40" s="5"/>
       <c r="G40" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H40" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H40" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I40" s="1">
         <f t="shared" si="1"/>
@@ -1817,12 +1796,12 @@
       <c r="D41" s="4"/>
       <c r="E41" s="5"/>
       <c r="G41" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H41" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H41" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I41" s="1">
         <f t="shared" si="1"/>
@@ -1835,12 +1814,12 @@
       <c r="D42" s="4"/>
       <c r="E42" s="5"/>
       <c r="G42" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H42" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H42" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I42" s="1">
         <f t="shared" si="1"/>
@@ -1853,12 +1832,12 @@
       <c r="D43" s="4"/>
       <c r="E43" s="5"/>
       <c r="G43" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H43" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H43" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I43" s="1">
         <f t="shared" si="1"/>
@@ -1871,12 +1850,12 @@
       <c r="D44" s="4"/>
       <c r="E44" s="5"/>
       <c r="G44" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H44" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H44" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I44" s="1">
         <f t="shared" si="1"/>
@@ -1889,12 +1868,12 @@
       <c r="D45" s="4"/>
       <c r="E45" s="5"/>
       <c r="G45" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H45" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H45" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I45" s="1">
         <f t="shared" si="1"/>
@@ -1907,12 +1886,12 @@
       <c r="D46" s="4"/>
       <c r="E46" s="5"/>
       <c r="G46" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H46" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H46" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I46" s="1">
         <f t="shared" si="1"/>
@@ -1925,12 +1904,12 @@
       <c r="D47" s="4"/>
       <c r="E47" s="5"/>
       <c r="G47" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H47" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H47" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I47" s="1">
         <f t="shared" si="1"/>
@@ -1943,12 +1922,12 @@
       <c r="D48" s="4"/>
       <c r="E48" s="5"/>
       <c r="G48" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H48" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H48" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I48" s="1">
         <f t="shared" si="1"/>
@@ -1961,12 +1940,12 @@
       <c r="D49" s="4"/>
       <c r="E49" s="5"/>
       <c r="G49" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H49" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H49" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I49" s="1">
         <f t="shared" si="1"/>
@@ -1979,12 +1958,12 @@
       <c r="D50" s="4"/>
       <c r="E50" s="5"/>
       <c r="G50" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H50" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H50" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I50" s="1">
         <f t="shared" si="1"/>
@@ -1997,12 +1976,12 @@
       <c r="D51" s="4"/>
       <c r="E51" s="5"/>
       <c r="G51" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H51" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H51" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I51" s="1">
         <f t="shared" si="1"/>
@@ -2015,12 +1994,12 @@
       <c r="D52" s="4"/>
       <c r="E52" s="5"/>
       <c r="G52" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H52" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H52" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I52" s="1">
         <f t="shared" si="1"/>
@@ -2033,12 +2012,12 @@
       <c r="D53" s="4"/>
       <c r="E53" s="5"/>
       <c r="G53" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H53" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H53" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I53" s="1">
         <f t="shared" si="1"/>
@@ -2051,12 +2030,12 @@
       <c r="D54" s="4"/>
       <c r="E54" s="5"/>
       <c r="G54" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H54" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H54" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I54" s="1">
         <f t="shared" si="1"/>
@@ -2069,12 +2048,12 @@
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
       <c r="G55" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H55" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H55" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I55" s="1">
         <f t="shared" si="1"/>
@@ -2087,12 +2066,12 @@
       <c r="D56" s="4"/>
       <c r="E56" s="5"/>
       <c r="G56" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H56" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H56" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I56" s="1">
         <f t="shared" si="1"/>
@@ -2105,12 +2084,12 @@
       <c r="D57" s="4"/>
       <c r="E57" s="5"/>
       <c r="G57" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H57" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H57" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I57" s="1">
         <f t="shared" si="1"/>
@@ -2123,12 +2102,12 @@
       <c r="D58" s="4"/>
       <c r="E58" s="5"/>
       <c r="G58" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H58" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H58" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I58" s="1">
         <f t="shared" si="1"/>
@@ -2141,12 +2120,12 @@
       <c r="D59" s="4"/>
       <c r="E59" s="5"/>
       <c r="G59" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H59" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H59" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I59" s="1">
         <f t="shared" si="1"/>
@@ -2156,12 +2135,12 @@
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="4"/>
       <c r="G60" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H60" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H60" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I60" s="1">
         <f t="shared" si="1"/>
@@ -2171,12 +2150,12 @@
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61" s="4"/>
       <c r="G61" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H61" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H61" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I61" s="1">
         <f t="shared" si="1"/>
@@ -2186,12 +2165,12 @@
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62" s="4"/>
       <c r="G62" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H62" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H62" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I62" s="1">
         <f t="shared" si="1"/>
@@ -2201,12 +2180,12 @@
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="4"/>
       <c r="G63" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H63" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H63" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I63" s="1">
         <f t="shared" si="1"/>
@@ -2216,12 +2195,12 @@
     <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64" s="4"/>
       <c r="G64" s="6" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H64" s="1" t="str">
-        <f t="shared" si="11"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H64" s="1" t="e">
+        <f t="shared" si="8"/>
+        <v>#REF!</v>
       </c>
       <c r="I64" s="1">
         <f t="shared" si="1"/>
@@ -2232,14 +2211,14 @@
       <c r="A65" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="17"/>
-      <c r="D65" s="16" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="17"/>
+      <c r="E65" s="12"/>
       <c r="F65" s="8" t="s">
         <v>4</v>
       </c>
@@ -2278,12 +2257,12 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G67" s="6" t="str">
-        <f t="shared" ref="G67:G98" si="12">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H67" s="1" t="str">
+        <f t="shared" ref="G67:G98" si="9">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H67" s="1" t="e">
         <f>IF(AND(G67&lt;&gt;" ",G67&lt;&gt;"ERROR",H64&lt;&gt;" ", H64&lt;&gt;"ERROR"),G67+H64," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>#REF!</v>
       </c>
       <c r="I67" s="1">
         <f t="shared" si="1"/>
@@ -2292,12 +2271,12 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G68" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H68" s="1" t="str">
-        <f t="shared" ref="H68:H98" si="13">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H68" s="1" t="e">
+        <f t="shared" ref="H68:H98" si="10">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
+        <v>#REF!</v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="1"/>
@@ -2306,421 +2285,421 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G69" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H69" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H69" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I69" s="1">
-        <f t="shared" ref="I69:I132" si="14">((D69+E69)-(B69+C69))*24</f>
+        <f t="shared" ref="I69:I132" si="11">((D69+E69)-(B69+C69))*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G70" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H70" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H70" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I70" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G71" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H71" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H71" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G72" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H72" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H72" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G73" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H73" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H73" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G74" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H74" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H74" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G75" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H75" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H75" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I75" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G76" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H76" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H76" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I76" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G77" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H77" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H77" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I77" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G78" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H78" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H78" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I78" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G79" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H79" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H79" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I79" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G80" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H80" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H80" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I80" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H81" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H81" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I81" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H82" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H82" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I82" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H83" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H83" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I83" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H84" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H84" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I84" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H85" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H85" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I85" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H86" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H86" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I86" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H87" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H87" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I87" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H88" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H88" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I88" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H89" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H89" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I89" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H90" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H90" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I90" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H91" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H91" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I91" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H92" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H92" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I92" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H93" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H93" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I93" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H94" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H94" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I94" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H95" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H95" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I95" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H96" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H96" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I96" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G97" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H97" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H97" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I97" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G98" s="6" t="str">
-        <f t="shared" si="12"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H98" s="1" t="str">
-        <f t="shared" si="13"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H98" s="1" t="e">
+        <f t="shared" si="10"/>
+        <v>#REF!</v>
       </c>
       <c r="I98" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -2728,14 +2707,14 @@
       <c r="A99" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="17"/>
-      <c r="D99" s="16" t="s">
+      <c r="C99" s="12"/>
+      <c r="D99" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="17"/>
+      <c r="E99" s="12"/>
       <c r="F99" s="8" t="s">
         <v>4</v>
       </c>
@@ -2746,7 +2725,7 @@
         <v>6</v>
       </c>
       <c r="I99" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2768,472 +2747,460 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
       <c r="I100" s="1" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G101" s="6" t="str">
-        <f t="shared" ref="G101:G132" si="15">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H101" s="1" t="str">
+        <f t="shared" ref="G101:G132" si="12">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H101" s="1" t="e">
         <f>IF(AND(G101&lt;&gt;" ",G101&lt;&gt;"ERROR",H98&lt;&gt;" ", H98&lt;&gt;"ERROR"),G101+H98," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>#REF!</v>
       </c>
       <c r="I101" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G102" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H102" s="1" t="str">
-        <f t="shared" ref="H102:H132" si="16">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ", H101&lt;&gt;"ERROR"),G102+H101," ")</f>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H102" s="1" t="e">
+        <f t="shared" ref="H102:H132" si="13">IF(AND(G102&lt;&gt;" ",G102&lt;&gt;"ERROR",H101&lt;&gt;" ", H101&lt;&gt;"ERROR"),G102+H101," ")</f>
+        <v>#REF!</v>
       </c>
       <c r="I102" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G103" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H103" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H103" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I103" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G104" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H104" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H104" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I104" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G105" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H105" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H105" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I105" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G106" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H106" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H106" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I106" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G107" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H107" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H107" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I107" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G108" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H108" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H108" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I108" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G109" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H109" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H109" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I109" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G110" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H110" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H110" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I110" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G111" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H111" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H111" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I111" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G112" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H112" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H112" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I112" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G113" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H113" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H113" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I113" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G114" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H114" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H114" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I114" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G115" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H115" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H115" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I115" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G116" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H116" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H116" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I116" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G117" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H117" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H117" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I117" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G118" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H118" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H118" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I118" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G119" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H119" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H119" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I119" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G120" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H120" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H120" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I120" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G121" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H121" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H121" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I121" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G122" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H122" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H122" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I122" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G123" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H123" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H123" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I123" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G124" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H124" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H124" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I124" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G125" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H125" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H125" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I125" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G126" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H126" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H126" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I126" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G127" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H127" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H127" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I127" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G128" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H128" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H128" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I128" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G129" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H129" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H129" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I129" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G130" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H130" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H130" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I130" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G131" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H131" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H131" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I131" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G132" s="6" t="str">
-        <f t="shared" si="15"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H132" s="1" t="str">
-        <f t="shared" si="16"/>
-        <v xml:space="preserve"> </v>
+        <f t="shared" si="12"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="H132" s="1" t="e">
+        <f t="shared" si="13"/>
+        <v>#REF!</v>
       </c>
       <c r="I132" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3247,6 +3214,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
